--- a/Data/DungeonEnhance.xlsx
+++ b/Data/DungeonEnhance.xlsx
@@ -8,20 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C246176F-79DF-4FBF-883C-17AE2E0D9AED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C142AE1-20EA-444E-AE99-14D843B35F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6345" yWindow="4110" windowWidth="25350" windowHeight="10530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DungeonEnhance" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="110">
   <si>
     <t>Stage</t>
   </si>
@@ -47,30 +46,12 @@
     <t>BossWeakDuration</t>
   </si>
   <si>
-    <t>RewardPointType1</t>
-  </si>
-  <si>
-    <t>RewardPointAmount1</t>
-  </si>
-  <si>
-    <t>RewardPointType2</t>
-  </si>
-  <si>
-    <t>RewardPointAmount2</t>
-  </si>
-  <si>
     <t>BossWeaknessCycle</t>
   </si>
   <si>
     <t>Enhance 1</t>
   </si>
   <si>
-    <t>Starforce</t>
-  </si>
-  <si>
-    <t>Gold</t>
-  </si>
-  <si>
     <t>Enhance 2</t>
   </si>
   <si>
@@ -216,6 +197,160 @@
   </si>
   <si>
     <t>Enhance 50</t>
+  </si>
+  <si>
+    <t>RewardPoints</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Starforce=9</t>
+  </si>
+  <si>
+    <t>Starforce=11</t>
+  </si>
+  <si>
+    <t>Starforce=13</t>
+  </si>
+  <si>
+    <t>Starforce=15</t>
+  </si>
+  <si>
+    <t>Starforce=17</t>
+  </si>
+  <si>
+    <t>Starforce=19</t>
+  </si>
+  <si>
+    <t>Starforce=21</t>
+  </si>
+  <si>
+    <t>Starforce=23</t>
+  </si>
+  <si>
+    <t>Starforce=25</t>
+  </si>
+  <si>
+    <t>Starforce=27</t>
+  </si>
+  <si>
+    <t>Starforce=29</t>
+  </si>
+  <si>
+    <t>Starforce=31</t>
+  </si>
+  <si>
+    <t>Starforce=33</t>
+  </si>
+  <si>
+    <t>Starforce=35</t>
+  </si>
+  <si>
+    <t>Starforce=37</t>
+  </si>
+  <si>
+    <t>Starforce=39</t>
+  </si>
+  <si>
+    <t>Starforce=41</t>
+  </si>
+  <si>
+    <t>Starforce=43</t>
+  </si>
+  <si>
+    <t>Starforce=45</t>
+  </si>
+  <si>
+    <t>Starforce=47</t>
+  </si>
+  <si>
+    <t>Starforce=49</t>
+  </si>
+  <si>
+    <t>Starforce=51</t>
+  </si>
+  <si>
+    <t>Starforce=53</t>
+  </si>
+  <si>
+    <t>Starforce=55</t>
+  </si>
+  <si>
+    <t>Starforce=57</t>
+  </si>
+  <si>
+    <t>Starforce=59</t>
+  </si>
+  <si>
+    <t>Starforce=61</t>
+  </si>
+  <si>
+    <t>Starforce=63</t>
+  </si>
+  <si>
+    <t>Starforce=65</t>
+  </si>
+  <si>
+    <t>Starforce=67</t>
+  </si>
+  <si>
+    <t>Starforce=69</t>
+  </si>
+  <si>
+    <t>Starforce=71</t>
+  </si>
+  <si>
+    <t>Starforce=73</t>
+  </si>
+  <si>
+    <t>Starforce=75</t>
+  </si>
+  <si>
+    <t>Starforce=77</t>
+  </si>
+  <si>
+    <t>Starforce=79</t>
+  </si>
+  <si>
+    <t>Starforce=81</t>
+  </si>
+  <si>
+    <t>Starforce=83</t>
+  </si>
+  <si>
+    <t>Starforce=85</t>
+  </si>
+  <si>
+    <t>Starforce=87</t>
+  </si>
+  <si>
+    <t>Starforce=89</t>
+  </si>
+  <si>
+    <t>Starforce=91</t>
+  </si>
+  <si>
+    <t>Starforce=93</t>
+  </si>
+  <si>
+    <t>Starforce=95</t>
+  </si>
+  <si>
+    <t>Starforce=97</t>
+  </si>
+  <si>
+    <t>Starforce=99</t>
+  </si>
+  <si>
+    <t>Starforce=101</t>
+  </si>
+  <si>
+    <t>Starforce=103</t>
+  </si>
+  <si>
+    <t>Starforce=105</t>
+  </si>
+  <si>
+    <t>Starforce=107</t>
   </si>
 </sst>
 </file>
@@ -562,10 +697,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -591,27 +729,18 @@
         <v>7</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D2">
         <v>110001</v>
@@ -629,27 +758,18 @@
         <v>1.82</v>
       </c>
       <c r="I2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2">
-        <v>9</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D3">
         <v>110002</v>
@@ -667,27 +787,18 @@
         <v>1.84</v>
       </c>
       <c r="I3" t="s">
-        <v>14</v>
-      </c>
-      <c r="J3">
-        <v>11</v>
-      </c>
-      <c r="K3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D4">
         <v>110003</v>
@@ -705,27 +816,18 @@
         <v>1.86</v>
       </c>
       <c r="I4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4">
-        <v>13</v>
-      </c>
-      <c r="K4" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" t="s">
         <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>18</v>
       </c>
       <c r="D5">
         <v>110004</v>
@@ -743,27 +845,18 @@
         <v>1.88</v>
       </c>
       <c r="I5" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5">
-        <v>15</v>
-      </c>
-      <c r="K5" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>110005</v>
@@ -781,27 +874,18 @@
         <v>1.9</v>
       </c>
       <c r="I6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6">
-        <v>17</v>
-      </c>
-      <c r="K6" t="s">
-        <v>15</v>
-      </c>
-      <c r="L6">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D7">
         <v>110006</v>
@@ -819,27 +903,18 @@
         <v>1.92</v>
       </c>
       <c r="I7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J7">
-        <v>19</v>
-      </c>
-      <c r="K7" t="s">
-        <v>15</v>
-      </c>
-      <c r="L7">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>110007</v>
@@ -857,27 +932,18 @@
         <v>1.94</v>
       </c>
       <c r="I8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8">
-        <v>21</v>
-      </c>
-      <c r="K8" t="s">
-        <v>15</v>
-      </c>
-      <c r="L8">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D9">
         <v>110008</v>
@@ -895,27 +961,18 @@
         <v>1.96</v>
       </c>
       <c r="I9" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9">
-        <v>23</v>
-      </c>
-      <c r="K9" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D10">
         <v>110009</v>
@@ -933,27 +990,18 @@
         <v>1.98</v>
       </c>
       <c r="I10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10">
-        <v>25</v>
-      </c>
-      <c r="K10" t="s">
-        <v>15</v>
-      </c>
-      <c r="L10">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D11">
         <v>110010</v>
@@ -971,27 +1019,18 @@
         <v>2</v>
       </c>
       <c r="I11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11">
-        <v>27</v>
-      </c>
-      <c r="K11" t="s">
-        <v>15</v>
-      </c>
-      <c r="L11">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="D12">
         <v>110011</v>
@@ -1009,27 +1048,18 @@
         <v>2.02</v>
       </c>
       <c r="I12" t="s">
-        <v>14</v>
-      </c>
-      <c r="J12">
-        <v>29</v>
-      </c>
-      <c r="K12" t="s">
-        <v>15</v>
-      </c>
-      <c r="L12">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D13">
         <v>110012</v>
@@ -1047,27 +1077,18 @@
         <v>2.04</v>
       </c>
       <c r="I13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13">
-        <v>31</v>
-      </c>
-      <c r="K13" t="s">
-        <v>15</v>
-      </c>
-      <c r="L13">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D14">
         <v>110013</v>
@@ -1085,27 +1106,18 @@
         <v>2.06</v>
       </c>
       <c r="I14" t="s">
-        <v>14</v>
-      </c>
-      <c r="J14">
-        <v>33</v>
-      </c>
-      <c r="K14" t="s">
-        <v>15</v>
-      </c>
-      <c r="L14">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C15" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D15">
         <v>110014</v>
@@ -1123,27 +1135,18 @@
         <v>2.08</v>
       </c>
       <c r="I15" t="s">
-        <v>14</v>
-      </c>
-      <c r="J15">
-        <v>35</v>
-      </c>
-      <c r="K15" t="s">
-        <v>15</v>
-      </c>
-      <c r="L15">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D16">
         <v>110015</v>
@@ -1161,27 +1164,18 @@
         <v>2.1</v>
       </c>
       <c r="I16" t="s">
-        <v>14</v>
-      </c>
-      <c r="J16">
-        <v>37</v>
-      </c>
-      <c r="K16" t="s">
-        <v>15</v>
-      </c>
-      <c r="L16">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C17" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D17">
         <v>110016</v>
@@ -1199,27 +1193,18 @@
         <v>2.12</v>
       </c>
       <c r="I17" t="s">
-        <v>14</v>
-      </c>
-      <c r="J17">
-        <v>39</v>
-      </c>
-      <c r="K17" t="s">
-        <v>15</v>
-      </c>
-      <c r="L17">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C18" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="D18">
         <v>110017</v>
@@ -1237,27 +1222,18 @@
         <v>2.14</v>
       </c>
       <c r="I18" t="s">
-        <v>14</v>
-      </c>
-      <c r="J18">
-        <v>41</v>
-      </c>
-      <c r="K18" t="s">
-        <v>15</v>
-      </c>
-      <c r="L18">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D19">
         <v>110018</v>
@@ -1275,27 +1251,18 @@
         <v>2.16</v>
       </c>
       <c r="I19" t="s">
-        <v>14</v>
-      </c>
-      <c r="J19">
-        <v>43</v>
-      </c>
-      <c r="K19" t="s">
-        <v>15</v>
-      </c>
-      <c r="L19">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D20">
         <v>110019</v>
@@ -1313,27 +1280,18 @@
         <v>2.1800000000000002</v>
       </c>
       <c r="I20" t="s">
-        <v>14</v>
-      </c>
-      <c r="J20">
-        <v>45</v>
-      </c>
-      <c r="K20" t="s">
-        <v>15</v>
-      </c>
-      <c r="L20">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C21" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>110020</v>
@@ -1351,27 +1309,18 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="I21" t="s">
-        <v>14</v>
-      </c>
-      <c r="J21">
-        <v>47</v>
-      </c>
-      <c r="K21" t="s">
-        <v>15</v>
-      </c>
-      <c r="L21">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C22" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D22">
         <v>110021</v>
@@ -1389,27 +1338,18 @@
         <v>2.2200000000000002</v>
       </c>
       <c r="I22" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22">
-        <v>49</v>
-      </c>
-      <c r="K22" t="s">
-        <v>15</v>
-      </c>
-      <c r="L22">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C23" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D23">
         <v>110022</v>
@@ -1427,27 +1367,18 @@
         <v>2.2400000000000002</v>
       </c>
       <c r="I23" t="s">
-        <v>14</v>
-      </c>
-      <c r="J23">
-        <v>51</v>
-      </c>
-      <c r="K23" t="s">
-        <v>15</v>
-      </c>
-      <c r="L23">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C24" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D24">
         <v>110023</v>
@@ -1465,27 +1396,18 @@
         <v>2.2599999999999998</v>
       </c>
       <c r="I24" t="s">
-        <v>14</v>
-      </c>
-      <c r="J24">
-        <v>53</v>
-      </c>
-      <c r="K24" t="s">
-        <v>15</v>
-      </c>
-      <c r="L24">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D25">
         <v>110024</v>
@@ -1503,27 +1425,18 @@
         <v>2.2799999999999998</v>
       </c>
       <c r="I25" t="s">
-        <v>14</v>
-      </c>
-      <c r="J25">
-        <v>55</v>
-      </c>
-      <c r="K25" t="s">
-        <v>15</v>
-      </c>
-      <c r="L25">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D26">
         <v>110025</v>
@@ -1541,27 +1454,18 @@
         <v>2.2999999999999998</v>
       </c>
       <c r="I26" t="s">
-        <v>14</v>
-      </c>
-      <c r="J26">
-        <v>57</v>
-      </c>
-      <c r="K26" t="s">
-        <v>15</v>
-      </c>
-      <c r="L26">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D27">
         <v>110026</v>
@@ -1579,27 +1483,18 @@
         <v>2.3199999999999998</v>
       </c>
       <c r="I27" t="s">
-        <v>14</v>
-      </c>
-      <c r="J27">
-        <v>59</v>
-      </c>
-      <c r="K27" t="s">
-        <v>15</v>
-      </c>
-      <c r="L27">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C28" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D28">
         <v>110027</v>
@@ -1617,27 +1512,18 @@
         <v>2.34</v>
       </c>
       <c r="I28" t="s">
-        <v>14</v>
-      </c>
-      <c r="J28">
-        <v>61</v>
-      </c>
-      <c r="K28" t="s">
-        <v>15</v>
-      </c>
-      <c r="L28">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C29" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D29">
         <v>110028</v>
@@ -1655,27 +1541,18 @@
         <v>2.36</v>
       </c>
       <c r="I29" t="s">
-        <v>14</v>
-      </c>
-      <c r="J29">
-        <v>63</v>
-      </c>
-      <c r="K29" t="s">
-        <v>15</v>
-      </c>
-      <c r="L29">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C30" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D30">
         <v>110029</v>
@@ -1693,27 +1570,18 @@
         <v>2.38</v>
       </c>
       <c r="I30" t="s">
-        <v>14</v>
-      </c>
-      <c r="J30">
-        <v>65</v>
-      </c>
-      <c r="K30" t="s">
-        <v>15</v>
-      </c>
-      <c r="L30">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C31" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D31">
         <v>110030</v>
@@ -1731,27 +1599,18 @@
         <v>2.4</v>
       </c>
       <c r="I31" t="s">
-        <v>14</v>
-      </c>
-      <c r="J31">
-        <v>67</v>
-      </c>
-      <c r="K31" t="s">
-        <v>15</v>
-      </c>
-      <c r="L31">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C32" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D32">
         <v>110031</v>
@@ -1769,27 +1628,18 @@
         <v>2.42</v>
       </c>
       <c r="I32" t="s">
-        <v>14</v>
-      </c>
-      <c r="J32">
-        <v>69</v>
-      </c>
-      <c r="K32" t="s">
-        <v>15</v>
-      </c>
-      <c r="L32">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C33" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D33">
         <v>110032</v>
@@ -1807,27 +1657,18 @@
         <v>2.44</v>
       </c>
       <c r="I33" t="s">
-        <v>14</v>
-      </c>
-      <c r="J33">
-        <v>71</v>
-      </c>
-      <c r="K33" t="s">
-        <v>15</v>
-      </c>
-      <c r="L33">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C34" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D34">
         <v>110033</v>
@@ -1845,27 +1686,18 @@
         <v>2.46</v>
       </c>
       <c r="I34" t="s">
-        <v>14</v>
-      </c>
-      <c r="J34">
-        <v>73</v>
-      </c>
-      <c r="K34" t="s">
-        <v>15</v>
-      </c>
-      <c r="L34">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C35" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D35">
         <v>110034</v>
@@ -1883,27 +1715,18 @@
         <v>2.48</v>
       </c>
       <c r="I35" t="s">
-        <v>14</v>
-      </c>
-      <c r="J35">
-        <v>75</v>
-      </c>
-      <c r="K35" t="s">
-        <v>15</v>
-      </c>
-      <c r="L35">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C36" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="D36">
         <v>110035</v>
@@ -1921,27 +1744,18 @@
         <v>2.5</v>
       </c>
       <c r="I36" t="s">
-        <v>14</v>
-      </c>
-      <c r="J36">
-        <v>77</v>
-      </c>
-      <c r="K36" t="s">
-        <v>15</v>
-      </c>
-      <c r="L36">
-        <v>1100</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C37" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D37">
         <v>110036</v>
@@ -1959,27 +1773,18 @@
         <v>2.52</v>
       </c>
       <c r="I37" t="s">
-        <v>14</v>
-      </c>
-      <c r="J37">
-        <v>79</v>
-      </c>
-      <c r="K37" t="s">
-        <v>15</v>
-      </c>
-      <c r="L37">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C38" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D38">
         <v>110037</v>
@@ -1997,27 +1802,18 @@
         <v>2.54</v>
       </c>
       <c r="I38" t="s">
-        <v>14</v>
-      </c>
-      <c r="J38">
-        <v>81</v>
-      </c>
-      <c r="K38" t="s">
-        <v>15</v>
-      </c>
-      <c r="L38">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C39" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="D39">
         <v>110038</v>
@@ -2035,27 +1831,18 @@
         <v>2.56</v>
       </c>
       <c r="I39" t="s">
-        <v>14</v>
-      </c>
-      <c r="J39">
-        <v>83</v>
-      </c>
-      <c r="K39" t="s">
-        <v>15</v>
-      </c>
-      <c r="L39">
-        <v>1184</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C40" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="D40">
         <v>110039</v>
@@ -2073,27 +1860,18 @@
         <v>2.58</v>
       </c>
       <c r="I40" t="s">
-        <v>14</v>
-      </c>
-      <c r="J40">
-        <v>85</v>
-      </c>
-      <c r="K40" t="s">
-        <v>15</v>
-      </c>
-      <c r="L40">
-        <v>1212</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C41" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D41">
         <v>110040</v>
@@ -2111,27 +1889,18 @@
         <v>2.6</v>
       </c>
       <c r="I41" t="s">
-        <v>14</v>
-      </c>
-      <c r="J41">
-        <v>87</v>
-      </c>
-      <c r="K41" t="s">
-        <v>15</v>
-      </c>
-      <c r="L41">
-        <v>1240</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C42" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D42">
         <v>110041</v>
@@ -2149,27 +1918,18 @@
         <v>2.62</v>
       </c>
       <c r="I42" t="s">
-        <v>14</v>
-      </c>
-      <c r="J42">
-        <v>89</v>
-      </c>
-      <c r="K42" t="s">
-        <v>15</v>
-      </c>
-      <c r="L42">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C43" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="D43">
         <v>110042</v>
@@ -2187,27 +1947,18 @@
         <v>2.64</v>
       </c>
       <c r="I43" t="s">
-        <v>14</v>
-      </c>
-      <c r="J43">
-        <v>91</v>
-      </c>
-      <c r="K43" t="s">
-        <v>15</v>
-      </c>
-      <c r="L43">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C44" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D44">
         <v>110043</v>
@@ -2225,27 +1976,18 @@
         <v>2.66</v>
       </c>
       <c r="I44" t="s">
-        <v>14</v>
-      </c>
-      <c r="J44">
-        <v>93</v>
-      </c>
-      <c r="K44" t="s">
-        <v>15</v>
-      </c>
-      <c r="L44">
-        <v>1324</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C45" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D45">
         <v>110044</v>
@@ -2263,27 +2005,18 @@
         <v>2.68</v>
       </c>
       <c r="I45" t="s">
-        <v>14</v>
-      </c>
-      <c r="J45">
-        <v>95</v>
-      </c>
-      <c r="K45" t="s">
-        <v>15</v>
-      </c>
-      <c r="L45">
-        <v>1352</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C46" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D46">
         <v>110045</v>
@@ -2301,27 +2034,18 @@
         <v>2.7</v>
       </c>
       <c r="I46" t="s">
-        <v>14</v>
-      </c>
-      <c r="J46">
-        <v>97</v>
-      </c>
-      <c r="K46" t="s">
-        <v>15</v>
-      </c>
-      <c r="L46">
-        <v>1380</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C47" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D47">
         <v>110046</v>
@@ -2339,27 +2063,18 @@
         <v>2.72</v>
       </c>
       <c r="I47" t="s">
-        <v>14</v>
-      </c>
-      <c r="J47">
-        <v>99</v>
-      </c>
-      <c r="K47" t="s">
-        <v>15</v>
-      </c>
-      <c r="L47">
-        <v>1408</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C48" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D48">
         <v>110047</v>
@@ -2377,27 +2092,18 @@
         <v>2.74</v>
       </c>
       <c r="I48" t="s">
-        <v>14</v>
-      </c>
-      <c r="J48">
-        <v>101</v>
-      </c>
-      <c r="K48" t="s">
-        <v>15</v>
-      </c>
-      <c r="L48">
-        <v>1436</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C49" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D49">
         <v>110048</v>
@@ -2415,27 +2121,18 @@
         <v>2.76</v>
       </c>
       <c r="I49" t="s">
-        <v>14</v>
-      </c>
-      <c r="J49">
-        <v>103</v>
-      </c>
-      <c r="K49" t="s">
-        <v>15</v>
-      </c>
-      <c r="L49">
-        <v>1464</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C50" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D50">
         <v>110049</v>
@@ -2453,27 +2150,18 @@
         <v>2.78</v>
       </c>
       <c r="I50" t="s">
-        <v>14</v>
-      </c>
-      <c r="J50">
-        <v>105</v>
-      </c>
-      <c r="K50" t="s">
-        <v>15</v>
-      </c>
-      <c r="L50">
-        <v>1492</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C51" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D51">
         <v>110050</v>
@@ -2491,16 +2179,7 @@
         <v>2.8</v>
       </c>
       <c r="I51" t="s">
-        <v>14</v>
-      </c>
-      <c r="J51">
-        <v>107</v>
-      </c>
-      <c r="K51" t="s">
-        <v>15</v>
-      </c>
-      <c r="L51">
-        <v>1520</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
